--- a/docs/test-cases/SPM-47_Test_Cases.xlsx
+++ b/docs/test-cases/SPM-47_Test_Cases.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="879" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="874" uniqueCount="236">
   <si>
     <t>Item</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Pre-conditions</t>
   </si>
   <si>
-    <t>Logged in as Hui Shan Neo (huishan.neo@connectsphere.com / password123), the Coordinator assigned to 'Pearl Delta Safety Conference' (status Planning, 14 Dec 2026 09:00-17:00, organised by Samuel Ong).
+    <t>Logged in as Hui Shan Neo (huishan.neo@connectsphere.com / password123), the Coordinator assigned to 'Pearl Delta Safety Conference' (status Planning, 4 Dec 2026 09:00-17:00, organised by Samuel Ong).
 The event already has one requirement: '4K Portable Projector', Quantity 4.</t>
   </si>
   <si>
@@ -846,26 +846,6 @@
   </si>
   <si>
     <t>With 'Afternoon workshop' chosen as the session, 'Audio Mixing Desk' was no longer offered in the Equipment dropdown. Switching the session back to 'Whole event' made it available again, confirming the filter is scoped to the chosen session rather than the whole event.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Logged in as Hui Shan Neo (huishan.neo@connectsphere.com / password123), the Coordinator assigned to 'Pearl Delta Safety Conference' (status Planning, 14 Dec 2026 09:00-17:00, organised by Samuel Ong).
-The event already has '4K Portable Projector' (Quantity 4) and 'Portable WiFi Access Point' (Quantity 4) for the whole event, and 'Audio Mixing Desk' (Quantity 1) for its 'Morning briefing' session.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The '4K Portable Projector' row is shown with Requested quantity 4, technical requirements 'Four demonstration stations.', and status 'Under review' — quantity and technical requirements as plain text, not an input field.
-No 'Save', 'Remove', or 'Add equipment' section are shown — the same read-only view as the Organiser gets.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Logged in as Joel Fernandez (joel.fernandez@connectsphere.com / password123), Coordinator of 'Pearl Delta Supplier Forum' (status Cancelled).
-A requirement was recorded for the event while it was still in Planning, and the event's status has since been set to Cancelled. Both are seeded by `npx prisma db seed`: the requirement is '4K Portable Projector', Quantity 2 (there is no in-app 'Cancel event' action yet).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Logged in as Hui Shan Neo (huishan.neo@connectsphere.com / password123), Coordinator of 'Pearl Delta Safety Conference'.
-The event has two sessions: 'Morning briefing' (09:00-12:00) and 'Afternoon workshop' (13:00-17:00), both on 14 Dec 2026. There is no in-app way to add a session to an existing event, so both sessions are seeded by `npx prisma db seed`.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Logged in as Hui Shan Neo (huishan.neo@connectsphere.com / password123), Coordinator of 'Pearl Delta Safety Conference', which has the two sessions from SPM-47-TC17.
-'Audio Mixing Desk' has already been requested for 'Morning briefing' (seeded).</t>
   </si>
 </sst>
 </file>
@@ -4156,7 +4136,7 @@
         <v>18</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>237</v>
+        <v>164</v>
       </c>
     </row>
     <row r="7" ht="17.25" customHeight="1">
@@ -11068,7 +11048,7 @@
         <v>7</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>238</v>
+        <v>202</v>
       </c>
     </row>
     <row r="4" ht="17.25" customHeight="1">
@@ -13380,7 +13360,7 @@
         <v>7</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>239</v>
+        <v>214</v>
       </c>
     </row>
     <row r="4" ht="125.25" customHeight="1">
@@ -14536,7 +14516,7 @@
         <v>7</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>236</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" ht="111.75" customHeight="1">
@@ -16848,7 +16828,7 @@
         <v>7</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>240</v>
+        <v>225</v>
       </c>
     </row>
     <row r="4" ht="44.25" customHeight="1">
